--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="22">
   <si>
     <t xml:space="preserve">4;3.5;2;0.5;</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -1,93 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Stage_Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">4;3.5;2;0.5;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10011;10012;10013;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10004;10005;10006;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10014;10015;10016;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10001;10002;10003;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5;3.5;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5;4;1.5;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;3;5;9;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40;60;60;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;4;6;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5;3;2;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5;4;1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;3;5;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1;3;6;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10007;10008;10009;10010;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_probability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -118,22 +50,17 @@
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="돋움"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="1" diagonalDown="1">
+    <border>
       <left>
         <color indexed="64"/>
       </left>
@@ -146,158 +73,162 @@
       <bottom>
         <color indexed="64"/>
       </bottom>
-      <diagonal>
-        <color indexed="64"/>
-      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="12">
+    <dxf/>
+    <dxf/>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
         </patternFill>
       </fill>
     </dxf>
+    <dxf/>
+    <dxf/>
+    <dxf/>
+    <dxf/>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
+          <fgColor rgb="FF94A5DF"/>
+          <bgColor rgb="FF94A5DF"/>
         </patternFill>
       </fill>
       <border>
-        <left style="thin">
-          <color rgb="FFBFBFBF"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFBFBFBF"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCE6F2"/>
-          <bgColor rgb="FFDCE6F2"/>
-        </patternFill>
-      </fill>
-      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
         <bottom style="thin">
-          <color rgb="FF96B3D7"/>
+          <color rgb="FF6182D6"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDCE6F2"/>
-          <bgColor rgb="FFDCE6F2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF96B3D7"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB8CCE5"/>
-          <bgColor rgb="FFB8CCE5"/>
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB8CCE5"/>
-          <bgColor rgb="FFB8CCE5"/>
-        </patternFill>
-      </fill>
-    </dxf>
+    <dxf/>
+    <dxf/>
+    <dxf/>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <tableStyleElement type="wholeTable" size="1"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </tableStyle>
+  </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -584,155 +515,246 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetPr codeName="Sheet1">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.5" customWidth="1"/>
-    <col min="4" max="4" width="23.92578125" customWidth="1"/>
-    <col min="5" max="5" width="24.92578125" customWidth="1"/>
-    <col min="6" max="6" width="25.78515625" customWidth="1"/>
-    <col min="7" max="7" width="20.2109375" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.92578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.92578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.78515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6171875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <v>base_inspection_time</v>
+        <is>
+          <t xml:space="preserve">base_inspection_time</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <v>station_count</v>
+        <is>
+          <t xml:space="preserve">station_count</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <v>stage_end_time</v>
+        <is>
+          <t xml:space="preserve">stage_end_time</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <v>spawn_interval</v>
+        <is>
+          <t xml:space="preserve">spawn_interval</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <v>spawn_monsters</v>
+        <is>
+          <t xml:space="preserve">spawn_monsters</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <v>spawn_monsters_probability</v>
+        <is>
+          <t xml:space="preserve">spawn_monsters_probability</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <v>spawn_monsters_level</v>
+        <is>
+          <t xml:space="preserve">spawn_monsters_level</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>50001</v>
+      </c>
+      <c r="B2" s="2">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
+      <c r="D2" s="2">
+        <v>180</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.312</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">10001;10002;10003;</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5;3;2;</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">1;3;5;</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1">
-        <v>50001</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1">
+    <row r="3">
+      <c r="A3" s="2">
+        <v>50002</v>
+      </c>
+      <c r="B3" s="2">
+        <v>40</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2">
         <v>180</v>
       </c>
-      <c r="D2" s="1">
-        <v>0.312</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
+      <c r="E3" s="2">
+        <v>0.72</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">10004;10005;10006;</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">4.5;4;1.5;</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">1;3;6;</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1">
-        <v>50002</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1">
+    <row r="4">
+      <c r="A4" s="2">
+        <v>50003</v>
+      </c>
+      <c r="B4" s="2">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
         <v>180</v>
       </c>
-      <c r="D3" s="1">
-        <v>0.71999999999999997</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
+      <c r="E4" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">10007;10008;10009;10010;</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">4;3.5;2;0.5;</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">1;3;5;9;</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1">
-        <v>50003</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="5">
+      <c r="A5" s="2">
+        <v>50004</v>
+      </c>
+      <c r="B5" s="2">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2">
         <v>180</v>
       </c>
-      <c r="D4" s="1">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>11</v>
+      <c r="E5" s="2">
+        <v>0.384</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">10011;10012;10013;</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5.5;3.5;1;</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">1;4;6;</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1">
-        <v>50004</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1">
+    <row r="6">
+      <c r="A6" s="2">
+        <v>50005</v>
+      </c>
+      <c r="B6" s="2">
+        <v>40</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
         <v>180</v>
       </c>
-      <c r="D5" s="1">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1">
-        <v>50005</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1">
-        <v>180</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.83999999999999997</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
+      <c r="E6" s="2">
+        <v>0.84</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">10014;10015;10016;</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5;4;1;</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">1;4;6;</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -13,7 +13,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t xml:space="preserve">spawn_monsters_elite_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spawn_monsters_elite_ramp</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,7 +526,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
@@ -581,6 +588,12 @@
           <t xml:space="preserve">spawn_monsters_level</t>
         </is>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
   <si>
     <t xml:space="preserve">spawn_monsters_elite_chance</t>
   </si>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -600,7 +600,7 @@
         <v>50001</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -635,7 +635,7 @@
         <v>50002</v>
       </c>
       <c r="B3" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
@@ -670,7 +670,7 @@
         <v>50003</v>
       </c>
       <c r="B4" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -705,7 +705,7 @@
         <v>50004</v>
       </c>
       <c r="B5" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -740,7 +740,7 @@
         <v>50005</v>
       </c>
       <c r="B6" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -626,7 +626,7 @@
       <c r="H2" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;3;5;</t>
+          <t xml:space="preserve">1;3;6;</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       <c r="H4" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;3;5;9;</t>
+          <t xml:space="preserve">1;3;5;8;</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -609,7 +609,7 @@
         <v>180</v>
       </c>
       <c r="E2" s="2">
-        <v>0.312</v>
+        <v>0.2857</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <v/>
@@ -620,13 +620,13 @@
       <c r="G2" s="2" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">5;3;2;</t>
+          <t xml:space="preserve">6;3;1;</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;3;6;</t>
+          <t xml:space="preserve">1;6;10;</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v>180</v>
       </c>
       <c r="E3" s="2">
-        <v>0.72</v>
+        <v>0.7143</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <v/>
@@ -655,13 +655,13 @@
       <c r="G3" s="2" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">4.5;4;1.5;</t>
+          <t xml:space="preserve">6;3;1;</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;3;6;</t>
+          <t xml:space="preserve">1;6;10;</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>180</v>
       </c>
       <c r="E4" s="2">
-        <v>0.6</v>
+        <v>0.5714</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <v/>
@@ -690,13 +690,13 @@
       <c r="G4" s="2" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">4;3.5;2;0.5;</t>
+          <t xml:space="preserve">6;3;1;0.5;</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;3;5;8;</t>
+          <t xml:space="preserve">1;6;10;15;</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
         <v>180</v>
       </c>
       <c r="E5" s="2">
-        <v>0.384</v>
+        <v>0.4286</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <v/>
@@ -725,13 +725,13 @@
       <c r="G5" s="2" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">5.5;3.5;1;</t>
+          <t xml:space="preserve">6;3;1;</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;4;6;</t>
+          <t xml:space="preserve">1;6;10;</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
         <v>180</v>
       </c>
       <c r="E6" s="2">
-        <v>0.84</v>
+        <v>0.8571</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <v/>
@@ -760,13 +760,13 @@
       <c r="G6" s="2" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">5;4;1;</t>
+          <t xml:space="preserve">6;3;1;</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">1;4;6;</t>
+          <t xml:space="preserve">1;6;10;</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -609,7 +609,7 @@
         <v>180</v>
       </c>
       <c r="E2" s="2">
-        <v>0.2857</v>
+        <v>0.2041</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <v/>
@@ -644,7 +644,7 @@
         <v>180</v>
       </c>
       <c r="E3" s="2">
-        <v>0.7143</v>
+        <v>0.5102</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <v/>
@@ -679,7 +679,7 @@
         <v>180</v>
       </c>
       <c r="E4" s="2">
-        <v>0.5714</v>
+        <v>0.4081</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <v/>
@@ -714,7 +714,7 @@
         <v>180</v>
       </c>
       <c r="E5" s="2">
-        <v>0.4286</v>
+        <v>0.3061</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <v/>
@@ -749,7 +749,7 @@
         <v>180</v>
       </c>
       <c r="E6" s="2">
-        <v>0.8571</v>
+        <v>0.6122</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <v/>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -1,61 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28545" windowHeight="11700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stage_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Stage_Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
-  <si>
-    <t xml:space="preserve">spawn_monsters_elite_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spawn_monsters_elite_ramp</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="6">
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
   </fonts>
   <fills count="2">
@@ -88,16 +78,14 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -521,257 +509,238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.92578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.92578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.78515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6171875" style="3" bestFit="1" customWidth="1"/>
+    <col width="9" customWidth="1" style="3" min="1" max="1"/>
+    <col width="21.140625" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14.5" customWidth="1" style="3" min="3" max="3"/>
+    <col width="23.92578125" customWidth="1" style="3" min="4" max="4"/>
+    <col width="24.92578125" customWidth="1" style="3" min="5" max="5"/>
+    <col width="25.78515625" customWidth="1" style="3" min="6" max="6"/>
+    <col width="24.9296875" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
+    <col width="19.6171875" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
-        <v>base_inspection_time</v>
-        <is>
-          <t xml:space="preserve">base_inspection_time</t>
+        <is>
+          <t>base_inspection_time</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
-        <v>station_count</v>
-        <is>
-          <t xml:space="preserve">station_count</t>
+        <is>
+          <t>station_count</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
-        <v>stage_end_time</v>
-        <is>
-          <t xml:space="preserve">stage_end_time</t>
+        <is>
+          <t>stage_end_time</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
-        <v>spawn_interval</v>
-        <is>
-          <t xml:space="preserve">spawn_interval</t>
+        <is>
+          <t>spawn_interval</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
-        <v>spawn_monsters</v>
-        <is>
-          <t xml:space="preserve">spawn_monsters</t>
+        <is>
+          <t>spawn_monsters</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
-        <v>spawn_monsters_probability</v>
-        <is>
-          <t xml:space="preserve">spawn_monsters_probability</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <v>spawn_monsters_level</v>
-        <is>
-          <t xml:space="preserve">spawn_monsters_level</t>
-        </is>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>1</v>
+        <is>
+          <t>spawn_monsters_probability</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>spawn_monsters_level</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>spawn_monsters_elite_chance</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>spawn_monsters_elite_ramp</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="2" t="n">
         <v>50001</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="2" t="n">
         <v>0.2041</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">10001;10002;10003;</t>
+        <is>
+          <t>10001;10002;10003;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">6;3;1;</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">1;6;10;</t>
+        <is>
+          <t>6;3;1;</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0;5;9;</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="2" t="n">
         <v>50002</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="2" t="n">
         <v>0.5102</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">10004;10005;10006;</t>
+        <is>
+          <t>10004;10005;10006;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">6;3;1;</t>
-        </is>
-      </c>
-      <c r="H3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">1;6;10;</t>
+        <is>
+          <t>6;3;1;</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0;5;9;</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="2" t="n">
         <v>50003</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="2" t="n">
         <v>0.4081</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">10007;10008;10009;10010;</t>
+        <is>
+          <t>10007;10008;10009;10010;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">6;3;1;0.5;</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">1;6;10;15;</t>
+        <is>
+          <t>6;3;1;0.5;</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0;5;9;14;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="2" t="n">
         <v>50004</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="2" t="n">
         <v>0.3061</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">10011;10012;10013;</t>
+        <is>
+          <t>10011;10012;10013;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">6;3;1;</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">1;6;10;</t>
+        <is>
+          <t>6;3;1;</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0;5;9;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="2" t="n">
         <v>50005</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="2" t="n">
         <v>0.6122</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">10014;10015;10016;</t>
+        <is>
+          <t>10014;10015;10016;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">6;3;1;</t>
-        </is>
-      </c>
-      <c r="H6" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">1;6;10;</t>
+        <is>
+          <t>6;3;1;</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0;5;9;</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0;5;9;</t>
+          <t>0;7;11;</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0;5;9;</t>
+          <t>0;7;11;</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0;5;9;14;</t>
+          <t>0;7;11;14;</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0;5;9;</t>
+          <t>0;7;11;</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0;5;9;</t>
+          <t>0;7;11;</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -587,13 +587,13 @@
         <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>180</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2041</v>
+        <v>0.2551</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -619,13 +619,13 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>180</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.5102</v>
+        <v>0.6378</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -651,13 +651,13 @@
         <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>180</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.4081</v>
+        <v>0.5101</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -683,13 +683,13 @@
         <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>180</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.3061</v>
+        <v>0.3826</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>180</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.6122</v>
+        <v>0.7653</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -587,7 +587,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>180</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0;7;11;</t>
+          <t>0;1;2;</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>180</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0;7;11;</t>
+          <t>8;8;8;</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>180</v>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0;7;11;14;</t>
+          <t>16;16;16;16;</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>180</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0;7;11;</t>
+          <t>4;4;6;</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>180</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0;7;11;</t>
+          <t>12;12;12;</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -593,7 +593,7 @@
         <v>180</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.2551</v>
+        <v>0.38</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>180</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.6378</v>
+        <v>0.64</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>180</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.5101</v>
+        <v>0.51</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         <v>180</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.3826</v>
+        <v>0.38</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>180</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.7653</v>
+        <v>0.77</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>

--- a/Assets/02_Resources/Data/StageData.xlsx
+++ b/Assets/02_Resources/Data/StageData.xlsx
@@ -514,7 +514,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col width="9" customWidth="1" style="3" min="1" max="1"/>
@@ -578,6 +578,11 @@
           <t>spawn_monsters_elite_ramp</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -610,6 +615,9 @@
           <t>0;1;2;</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -642,6 +650,9 @@
           <t>8;8;8;</t>
         </is>
       </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -674,6 +685,9 @@
           <t>16;16;16;16;</t>
         </is>
       </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -706,6 +720,9 @@
           <t>4;4;6;</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -737,6 +754,9 @@
         <is>
           <t>12;12;12;</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
